--- a/output/pdf_financials_xlsx/EPO.H.xlsx
+++ b/output/pdf_financials_xlsx/EPO.H.xlsx
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00195</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.019319</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2002,10 +2002,10 @@
         <v>-4.563154</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.664818</v>
+        <v>-5.666768</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.831964</v>
+        <v>-7.851283</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-8.46294</v>
@@ -2118,10 +2118,10 @@
         <v>-4.563154</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.664818</v>
+        <v>-5.666768</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.827095</v>
+        <v>-7.846414</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-8.457380000000001</v>
@@ -2422,55 +2422,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.183996</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.109594</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.109594</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>5.940458</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.279529</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.778728</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.778728</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.092779</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.156238</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.039203</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.003521</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.019982</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.000536</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.00115</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.160884</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.008781000000000001</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>6.600000000000001e-05</v>
       </c>
     </row>
     <row r="35">
@@ -2538,55 +2538,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.183996</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.109594</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.109594</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>5.940458</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.279529</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.778728</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.778728</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.092779</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.156238</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.039203</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.003521</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.019982</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.000536</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.00115</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.160884</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.008781000000000001</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>6.600000000000001e-05</v>
       </c>
     </row>
     <row r="37">
@@ -3237,52 +3237,52 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.246555</v>
+        <v>0.136961</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.246555</v>
+        <v>0.136961</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>6.332489</v>
+        <v>0.392031</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.710668</v>
+        <v>0.431139</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.901622</v>
+        <v>0.122894</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.901622</v>
+        <v>0.122894</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.116789</v>
+        <v>0.02401</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.170748</v>
+        <v>0.01451</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.052081</v>
+        <v>0.012878</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.006399</v>
+        <v>0.002878</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.028738</v>
+        <v>0.008756</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.012534</v>
+        <v>0.011998</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.019942</v>
+        <v>0.018792</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.172601</v>
+        <v>0.011717</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.028837</v>
+        <v>0.020056</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.026616</v>
+        <v>0.02655</v>
       </c>
     </row>
     <row r="49">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -18223,7 +18223,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
@@ -41148,7 +41148,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -43885,7 +43885,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -45272,7 +45272,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -47362,7 +47362,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -51400,7 +51400,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -54631,7 +54631,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -56037,7 +56037,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">

--- a/output/pdf_financials_xlsx/EPO.H.xlsx
+++ b/output/pdf_financials_xlsx/EPO.H.xlsx
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.080277</v>
+        <v>0.660428</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.081911</v>
+        <v>0.820968</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.008203</v>
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.520469</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.172982</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0.127361</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.080277</v>
+        <v>1.180897</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.081911</v>
+        <v>0.99395</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.135564</v>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.080277</v>
+        <v>-1.180897</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.081911</v>
+        <v>-0.99395</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-2.59927</v>
@@ -3358,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>2.014</v>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.001556</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.020943</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0.020943</v>
@@ -4030,7 +4030,7 @@
         <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>12.149184</v>
+        <v>10.029184</v>
       </c>
       <c r="E61" s="3" t="n">
         <v>30.543646</v>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0</v>
+        <v>0.040039</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0</v>
+        <v>0.012472</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>0</v>
@@ -5644,10 +5644,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>5.797886</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>14.483437</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>14.112359</v>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>2.070788</v>
@@ -20045,7 +20045,11 @@
           <t>Investment - Note 6</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -20447,7 +20451,11 @@
           <t>Share capital - Note 8</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -21362,7 +21370,11 @@
           <t>Equipment – Note 7</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E131" s="5" t="n">
         <v>0.001556</v>
       </c>
@@ -21663,7 +21675,11 @@
           <t>Due to related parties – Note 11</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="n">
         <v>0.040039</v>
       </c>
@@ -21863,7 +21879,11 @@
           <t>Share capital – Note 9</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="n">
         <v>5.797886</v>
       </c>
@@ -21962,7 +21982,11 @@
           <t>Contributed surplus – Note 9</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E137" s="5" t="n">
         <v>0.5901999999999999</v>
       </c>
@@ -53449,7 +53473,11 @@
           <t>Consulting fees - Note 10</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -53940,7 +53968,11 @@
           <t>Legal fees – Note 10</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr">
         <is>
           <t>-</t>
@@ -54039,7 +54071,11 @@
           <t>Management fees, salaries and benefits - Note 10</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>-</t>
@@ -54138,7 +54174,11 @@
           <t>Office - Note 10</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -55435,7 +55475,11 @@
           <t>Consulting fees – Note 11</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E480" s="5" t="n">
         <v>0.580151</v>
       </c>
@@ -55637,7 +55681,11 @@
           <t>Management fees, salaries and benefits – Note 11</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E482" s="5" t="n">
         <v>0.446628</v>
       </c>
@@ -55736,7 +55784,11 @@
           <t>Office – Note 11</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E483" s="5" t="n">
         <v>0.073841</v>
       </c>

--- a/output/pdf_financials_xlsx/EPO.H.xlsx
+++ b/output/pdf_financials_xlsx/EPO.H.xlsx
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-4.563154</v>
+        <v>-2.243078</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-5.664818</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2.29441</v>
+        <v>-0.025666</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>2.873409</v>
@@ -1366,19 +1366,19 @@
         <v>6.420056</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>7.872173</v>
+        <v>-2.557001</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.186675</v>
+        <v>-0.186675</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.105262</v>
+        <v>-0.105262</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.041</v>
+        <v>-0.041</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.196691</v>
+        <v>-0.196691</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>-0</v>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.563154</v>
+        <v>-2.243078</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-5.666768</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.563154</v>
+        <v>-2.243078</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-5.666768</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-50.28123092054312</v>
+        <v>-1.14423127506043</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-50.72376552962513</v>
@@ -2280,7 +2280,7 @@
         <v>-50.91196652337425</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-100</v>
+        <v>-32.48151431631393</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-1.812784141229262</v>
@@ -6351,13 +6351,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>1.036265</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0.025</v>
+        <v>0.135142</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.112495</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0</v>
@@ -6931,28 +6931,28 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00176</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000652</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000794</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001668</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.037233</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003608</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006142</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -8319,28 +8319,28 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00176</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000652</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000794</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001668</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.037233</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003608</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006142</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -8377,28 +8377,28 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.800575</v>
+        <v>-1.802335</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.606827</v>
+        <v>-1.607479</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.823717</v>
+        <v>-1.824511</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-2.975037</v>
+        <v>-2.976705</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-3.632223</v>
+        <v>-3.669456</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-4.149697</v>
+        <v>-4.153305</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-2.208553</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-2.622054</v>
+        <v>-2.628196</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-3.441373</v>
@@ -28251,7 +28251,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -30344,7 +30348,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -32136,7 +32144,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -33039,7 +33051,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -33138,7 +33154,11 @@
           <t>HST / GST recoverable</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -36067,7 +36087,11 @@
           <t>Private placements 30,816,666 7,988,708 108,292</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -37487,7 +37511,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -38097,7 +38125,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E300" s="5" t="n">
         <v>1.036265</v>
       </c>
@@ -38594,7 +38626,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E305" s="5" t="n">
         <v>-0.00176</v>
       </c>
@@ -45779,7 +45815,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -46905,7 +46945,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -48253,7 +48297,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -48926,7 +48974,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -52105,7 +52157,11 @@
           <t>Deferred income tax recovery (expense) 13</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>
@@ -55075,7 +55131,11 @@
           <t>Future income tax recovery – Note 11</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -56596,7 +56656,11 @@
           <t>Income tax recovery – Note 10</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E491" s="5" t="n">
         <v>0.025666</v>
       </c>
@@ -56697,7 +56761,11 @@
           <t>Future income tax recovery – Note 10</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
